--- a/student_assessment_forms/003_textile_knowledge_assessment--student_assessment_forms.xlsx
+++ b/student_assessment_forms/003_textile_knowledge_assessment--student_assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -684,7 +684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -870,12 +870,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>fiber</t>
+          <t>dye</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fiber</t>
+          <t>Dye</t>
         </is>
       </c>
     </row>
@@ -887,12 +887,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>dye</t>
+          <t>finishing</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dye</t>
+          <t>Finishing</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>finishing</t>
+          <t>knitting</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Finishing</t>
+          <t>Knitting</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>fabric</t>
+          <t>crochet</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Fabric</t>
+          <t>Crochet</t>
         </is>
       </c>
     </row>
@@ -938,12 +938,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>yarn</t>
+          <t>embroidery</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Yarn</t>
+          <t>Embroidery</t>
         </is>
       </c>
     </row>
@@ -955,12 +955,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>knitting</t>
+          <t>plying</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Knitting</t>
+          <t>Plying</t>
         </is>
       </c>
     </row>
@@ -972,12 +972,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>crochet</t>
+          <t>warp</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Crochet</t>
+          <t>Warp</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>embroidery</t>
+          <t>weave_structure</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Embroidery</t>
+          <t>Weave Structure</t>
         </is>
       </c>
     </row>
@@ -1006,12 +1006,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>plying</t>
+          <t>thread_count</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Plying</t>
+          <t>Thread Count</t>
         </is>
       </c>
     </row>
@@ -1023,12 +1023,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>warp</t>
+          <t>fiber_length</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Warp</t>
+          <t>Fiber Length</t>
         </is>
       </c>
     </row>
@@ -1040,12 +1040,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>weave_structure</t>
+          <t>yarn_count</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Weave Structure</t>
+          <t>Yarn Count</t>
         </is>
       </c>
     </row>
@@ -1057,12 +1057,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>thread_count</t>
+          <t>weight</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Thread Count</t>
+          <t>Weight</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>fiber_length</t>
+          <t>width</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Fiber Length</t>
+          <t>Width</t>
         </is>
       </c>
     </row>
@@ -1091,63 +1091,63 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yarn_count</t>
+          <t>length</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yarn Count</t>
+          <t>Length</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>general_knowledge_choices</t>
+          <t>assessment_1_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Weight</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>general_knowledge_choices</t>
+          <t>assessment_1_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>width</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>general_knowledge_choices</t>
+          <t>assessment_1_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>length</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1159,63 +1159,63 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>assessment_1_choices</t>
+          <t>assessment_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>assessment_1_choices</t>
+          <t>assessment_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>assessment_1_choices</t>
+          <t>assessment_2_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1227,61 +1227,10 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>assessment_2_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>assessment_2_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>assessment_2_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
         <is>
           <t>4</t>
         </is>
